--- a/output/2026-09-05_11_Italia_Sicilia_Cleaning.xlsx
+++ b/output/2026-09-05_11_Italia_Sicilia_Cleaning.xlsx
@@ -483,7 +483,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Filiale del gruppo PerPulire S.r.l. (sede legale Roma), attivo in Sicilia con filiali a Palermo e Messina. Macchine pulizia industriale, spazzatrici, lavasciuga, ingrosso prodotti pulizia. Indirizzo esatto filiale, telefono ed email non reperiti con certezza.</t>
@@ -491,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -528,7 +527,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -553,7 +552,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Vendita e noleggio macchine pulizia industriale (lavasciuga, monospazzole, macchine a vapore, idropulitrici). Attenzione: non confondere con l'omonima Cooperativa Sociale Le Ali della Vita (servizi pulizia, entita diversa).</t>
@@ -561,7 +559,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -598,7 +596,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -623,7 +621,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Strada Statale 192, 95121 Catania. Distributore esclusivo Sicilia orientale Adiatek e Isal; assistenza multibrand Cormac, Fiorentini, Fimap, Dulevo, Haco, Nilfisk.</t>
@@ -631,7 +628,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -668,7 +665,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -693,7 +690,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Contrada Cozzo delle Forche SNC, 96011 Augusta (SR). Rivenditore autorizzato Sicilia per Fiorentini e Dulevo - lavasciuga, spazzatrici, aspiratori.</t>
@@ -701,7 +697,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -738,7 +734,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -775,7 +771,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -812,7 +808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
